--- a/03_ai-threat-modeling-mitre-atlas/exercises/starter/threat_model_starter.xlsx
+++ b/03_ai-threat-modeling-mitre-atlas/exercises/starter/threat_model_starter.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring Rubric" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATLAS TTP Reference" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Family Reference" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATLAS Reference Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +45,10 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="7">
@@ -154,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -208,6 +213,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -968,17 +977,17 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — one sentence on how a deepfake / generative-liveness bypass shows up against FinTrust's mobile face-match KYC endpoint; reference the specific surface (selfie upload, liveness check, face-match model) and the recent competitor incident in the Scenario Brief.]</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 from the Scoring Rubric sheet; weigh how documented this attack class is against comparable KYC systems and FinTrust's public mobile exposure.]</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 from the Scoring Rubric sheet; weigh GDPR Art. 9 / EU AI Act exposure and financial-loss blast radius if a synthetic identity passes KYC.]</t>
         </is>
       </c>
       <c r="G4" s="11">
@@ -991,22 +1000,22 @@
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the primary family from the Control Family Reference sheet that binds at the pre-model input surface for this attack.]</t>
         </is>
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — list 2-3 named, concrete controls (e.g., specific liveness technique, challenge type, on-device check) that operationalize the family you picked in column I.]</t>
         </is>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the team that owns model-side defenses for FinTrust IDV (think about which role builds and tunes the face-match pipeline).]</t>
         </is>
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick a workflow status (e.g., Open / In Progress / Mitigated) consistent with a pre-launch threat model where the control is not yet built.]</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1037,17 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — one sentence on how model-extraction / membership-inference shows up against FinTrust's inference API; reference what an attacker gains (surrogate of the face-match embedder, recovery of enrolled biometrics).]</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 from the Scoring Rubric sheet; weigh attacker sophistication required vs. the fact that the API is public and already rate-limited per AML.T0040.]</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 from the Scoring Rubric sheet; weigh regulatory exposure (biometric data) and competitive loss from a surrogate model leaking.]</t>
         </is>
       </c>
       <c r="G5" s="11">
@@ -1051,22 +1060,22 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the family (or combination) from the Control Family Reference sheet best suited to detecting high-volume, pattern-based query abuse and capping API exposure.]</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — list 2-3 named controls (e.g., score quantization, daily query caps, extraction-pattern detection) that operationalize the family you picked in column I.]</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the team that owns inference-API defenses and model-side telemetry for FinTrust IDV.]</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick a workflow status consistent with a pre-launch threat model.]</t>
         </is>
       </c>
     </row>
@@ -1088,17 +1097,17 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — one sentence on how a data-poisoning attack shows up against FinTrust's monthly retrain pipeline; reference the production-queue ingestion path described in the Scenario Brief architecture.]</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 from the Scoring Rubric sheet; weigh how hard it is for an attacker to push enough poisoned samples through onboarding to move the model.]</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 from the Scoring Rubric sheet; weigh worst-case impact if the retrained model develops a targeted blind spot (KYC bypass at scale).]</t>
         </is>
       </c>
       <c r="G6" s="11">
@@ -1111,22 +1120,22 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the family from the Control Family Reference sheet that binds on the training / retrain ingestion path.]</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — list 2-3 named controls (e.g., outlier filtering, adversarial canary test set, model-promotion gate) that operationalize the family you picked in column I.]</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the team that owns the retrain pipeline and model-promotion gates for FinTrust IDV.]</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick a workflow status consistent with a pre-launch threat model.]</t>
         </is>
       </c>
     </row>
@@ -1221,22 +1230,22 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — TTP ID for rank 1 from your Threat Model sheet (highest Risk Score first; tie-break by Impact).]</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — TTP name matching the ID in column B; copy from the ATLAS TTP Reference sheet or your Threat Model row.]</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Risk Score from your Threat Model sheet (Likelihood × Impact) for this TTP.]</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Risk Level (Critical/High/Medium/Low) from the Scoring Rubric thresholds, matching the score in column D.]</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1255,22 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — TTP ID for rank 2 from your Threat Model sheet (highest Risk Score first; tie-break by Impact).]</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — TTP name matching the ID in column B; copy from the ATLAS TTP Reference sheet or your Threat Model row.]</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Risk Score from your Threat Model sheet (Likelihood × Impact) for this TTP.]</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Risk Level (Critical/High/Medium/Low) from the Scoring Rubric thresholds, matching the score in column D.]</t>
         </is>
       </c>
     </row>
@@ -1271,22 +1280,22 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — TTP ID for rank 3 from your Threat Model sheet (highest Risk Score first; tie-break by Impact).]</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — TTP name matching the ID in column B; copy from the ATLAS TTP Reference sheet or your Threat Model row.]</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Risk Score from your Threat Model sheet (Likelihood × Impact) for this TTP.]</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Risk Level (Critical/High/Medium/Low) from the Scoring Rubric thresholds, matching the score in column D.]</t>
         </is>
       </c>
     </row>
@@ -1319,13 +1328,13 @@
     <row r="12" ht="70" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>[TTP ID + name]</t>
+          <t>[Your response here — TTP ID + name matching the same-rank row in Section A above (e.g., 'AML.TXXXX — &lt;name&gt;').]</t>
         </is>
       </c>
       <c r="B12" s="14" t="n"/>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — 1–2 sentences naming the recommended controls and the residual risk after they are in place.]</t>
+          <t>[Your response here — 1-2 sentences naming the recommended controls for this TTP (drawn from your Threat Model column J / Control Family Reference) and stating the residual risk you expect after they are in place.]</t>
         </is>
       </c>
       <c r="D12" s="13" t="n"/>
@@ -1334,13 +1343,13 @@
     <row r="13" ht="70" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>[TTP ID + name]</t>
+          <t>[Your response here — TTP ID + name matching the same-rank row in Section A above (e.g., 'AML.TXXXX — &lt;name&gt;').]</t>
         </is>
       </c>
       <c r="B13" s="14" t="n"/>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — 1–2 sentences naming the recommended controls and the residual risk after they are in place.]</t>
+          <t>[Your response here — 1-2 sentences naming the recommended controls for this TTP (drawn from your Threat Model column J / Control Family Reference) and stating the residual risk you expect after they are in place.]</t>
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
@@ -1349,13 +1358,13 @@
     <row r="14" ht="70" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>[TTP ID + name]</t>
+          <t>[Your response here — TTP ID + name matching the same-rank row in Section A above (e.g., 'AML.TXXXX — &lt;name&gt;').]</t>
         </is>
       </c>
       <c r="B14" s="14" t="n"/>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — 1–2 sentences naming the recommended controls and the residual risk after they are in place.]</t>
+          <t>[Your response here — 1-2 sentences naming the recommended controls for this TTP (drawn from your Threat Model column J / Control Family Reference) and stating the residual risk you expect after they are in place.]</t>
         </is>
       </c>
       <c r="D14" s="13" t="n"/>
@@ -1380,7 +1389,7 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>[Launch / Conditional Launch / No-Go]</t>
+          <t>[Your response here — pick exactly one: Launch / Conditional Launch / No-Go.]</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -1393,7 +1402,7 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — one paragraph. Pick one of: Launch / Conditional Launch / No-Go. If Conditional, name the conditions in numbered form. Tie the recommendation back to the top TTPs and the residual-risk view above.]</t>
+          <t>[Your response here — one paragraph. Tie your decision back to your Top-3 TTPs and residual-risk view; if Conditional, list the specific pre-launch conditions (named controls + measurable gate) that must be met.]</t>
         </is>
       </c>
       <c r="C18" s="13" t="n"/>
@@ -1408,7 +1417,7 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>[Your name / role]</t>
+          <t>[Your response here — your name / role for the brief (e.g., 'AI Security Architect').]</t>
         </is>
       </c>
     </row>
@@ -2125,4 +2134,94 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>Specification detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>AML.T0048 sub-techniques</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>ATLAS structures External Harms (AML.T0048) into sub-techniques. The financial-loss case is captured precisely by AML.T0048.001 "Financial Harm" — ATLAS uses the term "Financial Harm" in the catalog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>AML.T0018 parent tactics</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>ATLAS lists Backdoor ML Model under both "Persistence" and "ML Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>AML.T0000 official name</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>The catalog name includes "for": "Search for Victim's Publicly Available Research Materials."</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>ML → AI naming evolution</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>ATLAS has been renaming the prefix from "ML" to "AI" in some technique names (e.g., AML.T0040 is "AI Model Inference API Access" in current revisions). Technique IDs are the stable canonical reference; treat the ID as authoritative when the name on the live catalog differs from the workbook label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Authoritative reference</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>See https://atlas.mitre.org/ and per-technique pages (e.g., https://atlas.mitre.org/techniques/AML.T0048/).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/03_ai-threat-modeling-mitre-atlas/exercises/starter/threat_model_starter.xlsx
+++ b/03_ai-threat-modeling-mitre-atlas/exercises/starter/threat_model_starter.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -157,10 +157,10 @@
     <t xml:space="preserve">AML.T0040</t>
   </si>
   <si>
-    <t xml:space="preserve">ML Model Inference API Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ML Model Access</t>
+    <t xml:space="preserve">AI Model Inference API Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Model Access</t>
   </si>
   <si>
     <t xml:space="preserve">The face-match endpoint is exposed via the mobile-app gateway; once an attacker has passed app attestation, they can query the model with arbitrary image pairs and observe similarity scores, providing the substrate for downstream evasion or extraction attacks.</t>
@@ -175,7 +175,7 @@
     <t xml:space="preserve">AML.T0015</t>
   </si>
   <si>
-    <t xml:space="preserve">Evade ML Model — Deepfake / Generative-Liveness Bypass</t>
+    <t xml:space="preserve">Evade AI Model — Deepfake / Generative-Liveness Bypass</t>
   </si>
   <si>
     <t xml:space="preserve">Defense Evasion / Initial Access</t>
@@ -205,7 +205,7 @@
     <t xml:space="preserve">AML.T0024</t>
   </si>
   <si>
-    <t xml:space="preserve">Exfiltration via ML Inference API</t>
+    <t xml:space="preserve">Exfiltration via AI Inference API</t>
   </si>
   <si>
     <t xml:space="preserve">Exfiltration</t>
@@ -433,7 +433,7 @@
     <t xml:space="preserve">Adversary probes the AI system's API surface — endpoints, rate limits, auth — to map the attack surface.</t>
   </si>
   <si>
-    <t xml:space="preserve">Evade ML Model</t>
+    <t xml:space="preserve">Evade AI Model</t>
   </si>
   <si>
     <t xml:space="preserve">Adversary crafts inputs designed to be misclassified by the model (adversarial / presentation / prompt-evasion attacks).</t>
@@ -442,7 +442,7 @@
     <t xml:space="preserve">AML.T0018</t>
   </si>
   <si>
-    <t xml:space="preserve">Backdoor ML Model</t>
+    <t xml:space="preserve">Backdoor AI Model</t>
   </si>
   <si>
     <t xml:space="preserve">Persistence</t>
@@ -460,7 +460,7 @@
     <t xml:space="preserve">AML.T0029</t>
   </si>
   <si>
-    <t xml:space="preserve">Denial of ML Service</t>
+    <t xml:space="preserve">Denial of AI Service</t>
   </si>
   <si>
     <t xml:space="preserve">Impact</t>
@@ -487,7 +487,7 @@
     <t xml:space="preserve">AML.T0044</t>
   </si>
   <si>
-    <t xml:space="preserve">Full ML Model Access</t>
+    <t xml:space="preserve">Full AI Model Access</t>
   </si>
   <si>
     <t xml:space="preserve">Adversary obtains direct access to model weights, enabling any white-box attack.</t>
@@ -586,7 +586,7 @@
     <t xml:space="preserve">AML.T0018 parent tactics</t>
   </si>
   <si>
-    <t xml:space="preserve">ATLAS lists Backdoor ML Model under both "Persistence" and "ML Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
+    <t xml:space="preserve">ATLAS lists Backdoor AI Model under both "Persistence" and "ML Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
   </si>
   <si>
     <t xml:space="preserve">AML.T0000 official name</t>
@@ -759,87 +759,87 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -923,34 +923,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1096,7 +1096,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="110"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
@@ -1107,119 +1107,119 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
         <v>21</v>
       </c>
@@ -1241,7 +1241,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
@@ -1511,7 +1511,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
@@ -1548,7 +1548,7 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>81</v>
       </c>
@@ -1678,7 +1678,7 @@
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
         <v>94</v>
       </c>
@@ -1698,7 +1698,7 @@
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
     </row>
-    <row r="20" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
         <v>98</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
         <v>100</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
         <v>102</v>
       </c>
@@ -1756,7 +1756,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="95"/>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B1" s="9"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
         <v>105</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
         <v>107</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
         <v>109</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
         <v>111</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
         <v>113</v>
       </c>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B8" s="9"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
         <v>105</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
         <v>107</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
         <v>109</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
         <v>111</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
         <v>113</v>
       </c>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
         <v>122</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
         <v>124</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
         <v>126</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
         <v>128</v>
       </c>
@@ -1914,7 +1914,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50"/>
@@ -2135,7 +2135,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="110"/>
@@ -2230,13 +2230,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="110"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
         <v>181</v>
       </c>

--- a/03_ai-threat-modeling-mitre-atlas/exercises/starter/threat_model_starter.xlsx
+++ b/03_ai-threat-modeling-mitre-atlas/exercises/starter/threat_model_starter.xlsx
@@ -478,7 +478,7 @@
     <t xml:space="preserve">Craft Adversarial Data</t>
   </si>
   <si>
-    <t xml:space="preserve">ML Attack Staging</t>
+    <t xml:space="preserve">AI Attack Staging</t>
   </si>
   <si>
     <t xml:space="preserve">Adversary generates adversarial examples (white-box, black-box, or transfer) targeting the deployed model.</t>
@@ -586,7 +586,7 @@
     <t xml:space="preserve">AML.T0018 parent tactics</t>
   </si>
   <si>
-    <t xml:space="preserve">ATLAS lists Backdoor AI Model under both "Persistence" and "ML Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
+    <t xml:space="preserve">ATLAS lists Backdoor AI Model under both "Persistence" and "AI Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
   </si>
   <si>
     <t xml:space="preserve">AML.T0000 official name</t>
